--- a/aq_files/0102.xlsx
+++ b/aq_files/0102.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A researcher distributes questionnaires via email to collect responses from participants. Which method of data collection is used?</t>
-  </si>
-  <si>
-    <t>A surveyor visits households and asks questions face-to-face. Identify the data collection method.</t>
-  </si>
-  <si>
-    <t>A company collects customer feedback through an online Google Form. What method is this?</t>
-  </si>
-  <si>
-    <t>A researcher gathers data by directly observing customer behavior in a store without interacting with them. What method is used?</t>
-  </si>
-  <si>
-    <t>A census worker collects data from every household in a country. What type of data collection method is this?</t>
-  </si>
-  <si>
-    <t>A researcher records answers by calling participants over the phone. Identify the method used.</t>
-  </si>
-  <si>
-    <t>A scientist collects data from already published research papers and reports. What type of data collection is this?</t>
-  </si>
-  <si>
-    <t>A company installs cameras to observe how customers move inside a store. What method of data collection is applied?</t>
-  </si>
-  <si>
-    <t>A teacher collects data by asking students to fill out a printed questionnaire. What method is used?</t>
-  </si>
-  <si>
-    <t>A researcher conducts in-depth one-on-one discussions with participants. Identify the method.</t>
-  </si>
-  <si>
-    <t>A government collects population data from all citizens during a nationwide survey. What method is this?</t>
-  </si>
-  <si>
-    <t>A researcher collects data from books, journals, and websites instead of direct interaction. What type of data is this?</t>
-  </si>
-  <si>
-    <t>A company collects feedback using suggestion boxes placed in stores. What method is used?</t>
-  </si>
-  <si>
-    <t>A researcher gathers data by participating in group activities and observing behavior. Identify the method.</t>
-  </si>
-  <si>
-    <t>A survey collects data by sending SMS-based questionnaires. What method is this?</t>
-  </si>
-  <si>
-    <t>A researcher studies past records of a hospital to collect patient data. What type of data collection is used?</t>
-  </si>
-  <si>
-    <t>A company collects customer opinions through social media polls. What method is applied?</t>
-  </si>
-  <si>
-    <t>A researcher personally asks structured questions and records answers during interviews. What method is this?</t>
-  </si>
-  <si>
-    <t>A study collects data by measuring temperature and recording it directly using instruments. What method is used?</t>
-  </si>
-  <si>
-    <t>A researcher combines observation and interviews to gather detailed information. What type of data collection approach is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1333 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order_ID,Order_Date,Region,State,City,Product_Category,Sub_Category,Product_Name,Sales,Quantity,Profit,Discount,Shipping_Cost,Customer_Segment</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3001,2024-01-01,North,Illinois,Chicago,Electronics,Computers,MacBook Pro,2499.99,2,749.98,0.10,25.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3002,2024-01-01,North,Illinois,Chicago,Electronics,Accessories,Magic Mouse,89.99,5,179.98,0.05,8.50,Corporate</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3003,2024-01-02,South,Texas,Houston,Clothing,Mens,Designer Jeans,99.99,8,399.96,0.00,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3004,2024-01-02,South,Texas,Austin,Electronics,Monitors,4K Monitor,449.99,3,674.98,0.15,18.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3005,2024-01-03,East,New York,New York,Furniture,Chairs,Executive Chair,449.99,2,449.98,0.05,22.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3006,2024-01-03,East,New York,Buffalo,Electronics,Keyboards,Mechanical Keyboard,129.99,4,259.96,0.10,10.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3007,2024-01-04,West,California,Los Angeles,Clothing,Womens,Leather Jacket,199.99,3,299.98,0.20,15.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3008,2024-01-04,West,California,San Francisco,Electronics,Tablets,iPad Air,599.99,2,599.98,0.05,20.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3009,2024-01-05,North,Illinois,Chicago,Furniture,Lighting,Floor Lamp,89.99,5,224.98,0.00,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3010,2024-01-05,North,Michigan,Detroit,Clothing,Mens,Running Shoes,79.99,6,239.97,0.10,10.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3011,2024-01-06,South,Texas,Dallas,Electronics,Computers,Gaming Laptop,1599.99,1,399.99,0.15,25.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3012,2024-01-06,East,Pennsylvania,Philadelphia,Electronics,Audio,Headphones,199.99,3,299.98,0.05,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3013,2024-01-07,West,California,San Diego,Clothing,Womens,Wool Coat,249.99,2,249.98,0.20,15.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3014,2024-01-07,North,Ohio,Columbus,Furniture,Storage,Bookshelf,189.99,2,189.98,0.10,18.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3015,2024-01-08,South,Florida,Miami,Electronics,Phones,Smartphone,799.99,3,1199.98,0.05,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3016,2024-01-08,East,New York,New York,Clothing,Mens,Dress Shirt,69.99,8,279.96,0.00,10.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3017,2024-01-09,West,Oregon,Portland,Electronics,Storage,External SSD,129.99,3,194.98,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3018,2024-01-09,North,Illinois,Chicago,Clothing,Womens,Hoodie,59.99,10,299.95,0.05,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3019,2024-01-10,South,Texas,Austin,Furniture,Desks,Gaming Desk,399.99,1,199.99,0.15,25.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3020,2024-01-10,East,Massachusetts,Boston,Electronics,Accessories,Webcam,89.99,4,179.98,0.10,8.50,Home Office</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3021,2024-01-11,West,Washington,Seattle,Electronics,Docks,Docking Station,149.99,3,224.98,0.00,10.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3022,2024-01-11,North,Minnesota,Minneapolis,Clothing,Mens,Winter Parka,199.99,3,299.98,0.05,15.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3023,2024-01-12,South,Florida,Orlando,Furniture,Desks,Office Desk,499.99,2,499.98,0.10,22.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3024,2024-01-12,East,New Jersey,Newark,Electronics,Cables,USB-C Hub,49.99,8,199.96,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3025,2024-01-13,West,California,Los Angeles,Clothing,Mens,Casual Blazer,159.99,4,319.98,0.15,12.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3026,2024-01-13,North,Indiana,Indianapolis,Electronics,Accessories,Gaming Mouse,69.99,8,279.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3027,2024-01-14,South,Georgia,Atlanta,Electronics,Printers,Laser Printer,249.99,2,249.98,0.05,18.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3028,2024-01-14,East,Virginia,Richmond,Furniture,Chairs,Lounge Chair,329.99,2,329.98,0.20,22.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3029,2024-01-15,West,Arizona,Phoenix,Electronics,Batteries,Power Bank,59.99,12,359.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3030,2024-01-15,North,Wisconsin,Milwaukee,Clothing,Accessories,Wool Scarf,29.99,15,224.85,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3031,2024-02-01,South,Texas,Houston,Electronics,Audio,Gaming Headset,139.99,4,279.98,0.05,12.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3032,2024-02-01,East,New York,Rochester,Furniture,Storage,Night Stand,89.99,5,224.98,0.10,15.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3033,2024-02-02,West,California,San Jose,Clothing,Mens,Athletic Shoes,119.99,4,239.98,0.15,10.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3034,2024-02-02,North,Missouri,St Louis,Electronics,Wearables,Smart Watch,249.99,3,374.98,0.05,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3035,2024-02-03,South,Florida,Tampa,Electronics,Audio,Bluetooth Speaker,99.99,6,299.97,0.10,10.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3036,2024-02-03,East,Pennsylvania,Pittsburgh,Clothing,Womens,Cashmere Sweater,129.99,5,324.97,0.00,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3037,2024-02-04,West,Oregon,Eugene,Furniture,Storage,Bookshelf,159.99,3,239.98,0.05,18.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3038,2024-02-04,North,Iowa,Des Moines,Electronics,Networking,Mesh Router,119.99,4,239.98,0.10,10.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3039,2024-02-05,South,Texas,San Antonio,Clothing,Mens,Golf Polo,49.99,12,299.94,0.15,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3040,2024-02-05,West,Washington,Spokane,Electronics,Components,Graphics Card,549.99,2,549.98,0.20,18.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3041,2024-02-06,North,Illinois,Chicago,Electronics,Keyboards,Wireless Keyboard,79.99,6,239.97,0.05,8.50,Corporate</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3042,2024-02-06,South,Texas,Austin,Clothing,Accessories,Running Socks,14.99,20,149.90,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3043,2024-02-07,East,New York,New York,Furniture,Tables,Coffee Table,279.99,2,279.98,0.15,22.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3044,2024-02-07,West,California,Los Angeles,Electronics,Smart Home,Smart Speaker,129.99,5,324.97,0.00,10.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3045,2024-02-08,North,Michigan,Detroit,Clothing,Accessories,Baseball Cap,24.99,20,249.90,0.05,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3046,2024-02-08,South,Florida,Miami,Electronics,Drones,Quadcopter,399.99,2,399.98,0.10,18.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3047,2024-02-09,East,Pennsylvania,Philadelphia,Furniture,Decor,Wall Mirror,79.99,6,239.97,0.00,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3048,2024-02-09,West,Oregon,Portland,Clothing,Mens,Flannel Shirt,54.99,8,219.96,0.15,10.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3049,2024-02-10,North,Ohio,Columbus,Electronics,Streaming,Streaming Stick,49.99,8,199.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3050,2024-02-10,South,Georgia,Atlanta,Clothing,Womens,Yoga Pants,44.99,12,269.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3051,2024-02-11,West,California,Los Angeles,Electronics,Monitors,Ultrawide Monitor,549.99,2,549.98,0.15,22.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3052,2024-02-11,North,Illinois,Chicago,Clothing,Mens,Denim Jacket,89.99,5,224.98,0.10,12.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3053,2024-02-12,South,Texas,Houston,Furniture,Chairs,Gaming Chair,299.99,2,299.98,0.05,22.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3054,2024-02-12,East,New York,Buffalo,Electronics,Audio,Portable Speaker,79.99,4,159.98,0.00,10.00,Consumer</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3055,2024-02-13,West,Washington,Seattle,Clothing,Womens,Rain Jacket,129.99,3,194.98,0.15,12.00,Home Office</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3056,2024-02-13,North,Minnesota,Minneapolis,Electronics,Storage,Portable SSD,89.99,5,224.98,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3057,2024-02-14,South,Florida,Orlando,Electronics,Phones,Smartphone Case,29.99,15,224.85,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3058,2024-02-14,East,Massachusetts,Boston,Furniture,Lighting,Desk Lamp,59.99,6,179.97,0.05,12.00,Corporate</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3059,2024-02-15,West,California,San Diego,Clothing,Accessories,Leather Belt,39.99,8,159.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3060,2024-02-15,North,Ohio,Columbus,Electronics,Accessories,Phone Stand,19.99,12,119.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a Horizontal Bar Chart showing total Sales by Product Category (Electronics, Clothing, Furniture). Sort the bars in descending order. Which category has the highest sales? What is the total sales value?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Create a Horizontal Bar Chart showing total Profit by Product Category. Which category is the most profitable? Which category has the lowest profit?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a Horizontal Bar Chart showing total Quantity Sold by Product Category. Which category sells the most units? What is the total quantity?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a Horizontal Bar Chart showing total Sales by Top 10 Products. Which product is the best-selling? What is its total sales value?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a Horizontal Bar Chart showing total Sales by State. Which 5 states have the highest sales? Which state has the lowest sales?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a Horizontal Bar Chart showing total Sales by Customer Segment (Corporate, Consumer, Home Office). Which segment contributes the most to sales?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a Horizontal Bar Chart showing total Sales by Sub-Category (Computers, Monitors, Keyboards, Audio, Phones, etc.). Which sub-category has the highest sales?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a Tree Map showing total Sales by Product Category and Sub-Category. Which combination has the largest area (highest sales)? Which has the smallest?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a Tree Map showing total Profit by Product Category and Sub-Category. Which sub-category generates the highest profit?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a Tree Map showing total Sales by Region and State. Which state has the largest area? Which region has the most states with high sales?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a Tree Map showing total Quantity Sold by Product Category and Product Name. Which product has the largest area (highest quantity sold)?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a Tree Map showing total Sales by Customer Segment and Product Category. Which combination (Segment-Category) has the largest area?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a Line Chart showing total Sales by Order Date (daily) for the month of January. Identify the day with the highest sales. What was the sales value?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a Line Chart showing total Sales by Order Date (daily) with a trend line. Is there an upward or downward trend from January 1 to February 15?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a Line Chart showing total Sales by Week (Week 1-6). Which week had the highest sales? Which week had the lowest?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a Line Chart with multiple lines showing Sales by Product Category over time (daily). Which category shows the most consistent performance? Which shows the most volatility?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a Line Chart showing total Sales by Order Date with a reference line for average sales. Which days are above average? Which days are below average?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a Dual Line Chart showing Sales (line) and Profit Margin % (line) over time. What relationship do you observe between sales and profit margin?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a Line Chart showing cumulative Sales (running total) by Order Date. What was the total cumulative sales by January 31? By February 15?</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Bar chart, Tree Map, Line Chart</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Dashboard with three visualizations: (1) Bar Chart: Sales by Category, (2) Tree Map: Sales by Category and Sub-Category, (3) Line Chart: Sales Trend over Time. Add a quick filter for Region that controls all three charts. How does filtering by 'West' region change the Tree Map?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>